--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B80FA55-8D65-4A5A-8A89-E8C3D830E17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711151BE-6D95-4C00-A498-6F73CADD12BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="170">
   <si>
     <t>Field</t>
   </si>
@@ -70,6 +70,9 @@
     <t>CurrentGrade</t>
   </si>
   <si>
+    <t>Elementary School</t>
+  </si>
+  <si>
     <t>Interests</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>Intro</t>
   </si>
   <si>
+    <t>A warm portfolio that records Richard's learning journey, works, awards, reading, and yearly growth.</t>
+  </si>
+  <si>
     <t>HeroImage</t>
   </si>
   <si>
@@ -88,6 +94,9 @@
     <t>PrivacyNote</t>
   </si>
   <si>
+    <t>Use nickname only. Avoid full school name, class, address, birthday, and other personal information.</t>
+  </si>
+  <si>
     <t>LastUpdated</t>
   </si>
   <si>
@@ -118,391 +127,432 @@
     <t>Privacy</t>
   </si>
   <si>
+    <t>AwardName</t>
+  </si>
+  <si>
+    <t>AwardLevel</t>
+  </si>
+  <si>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>International Joint Schools Mathematics Competition (IJSMC)</t>
+  </si>
+  <si>
+    <t>TOP TALENT AWARD</t>
+  </si>
+  <si>
+    <t>Asian Gifted Education Association</t>
+  </si>
+  <si>
+    <t>Richard joined the International Joint Schools Mathematics Competition and received the Top Talent Award. This experience encouraged him to think deeply, solve problems with confidence, and enjoy mathematical challenges.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>MATH KANGAROO TAIWAN</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Association Kangourou sans Frontières</t>
+  </si>
+  <si>
+    <t>Richard participated in Math Kangaroo Taiwan and earned a Silver Award. This experience helped him build confidence in mathematical thinking and problem-solving.</t>
+  </si>
+  <si>
+    <t>award_001.jpg</t>
+  </si>
+  <si>
+    <t>第63屆 奧林匹克數理競賽</t>
+  </si>
+  <si>
+    <t>金卓越銀獎</t>
+  </si>
+  <si>
+    <t>中華數學協會</t>
+  </si>
+  <si>
+    <t>Richard participated in the 63rd Olympic Mathematics and Science Competition and received the Gold Excellence Silver Award. The experience helped him build focus, patience, and confidence in mathematical problem-solving.</t>
+  </si>
+  <si>
+    <t>ProjectName</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>VideoLink</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>Scratch Fruit Catcher Game</t>
+  </si>
+  <si>
+    <t>A simple game where the player catches falling fruit and avoids obstacles.</t>
+  </si>
+  <si>
+    <t>Scratch</t>
+  </si>
+  <si>
+    <t>project_001.jpg</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>My Favorite Animal Drawing</t>
+  </si>
+  <si>
+    <t>An illustrated animal drawing with a short description.</t>
+  </si>
+  <si>
+    <t>Color pencils</t>
+  </si>
+  <si>
+    <t>project_002.jpg</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>Mini Weather Chart</t>
+  </si>
+  <si>
+    <t>Recorded weather changes and summarized temperature patterns.</t>
+  </si>
+  <si>
+    <t>Notebook, chart</t>
+  </si>
+  <si>
+    <t>BookTitle</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Amazing Insects</t>
+  </si>
+  <si>
+    <t>Sample Author</t>
+  </si>
+  <si>
+    <t>I learned that insects use many ways to protect themselves.</t>
+  </si>
+  <si>
+    <t>book_001.jpg</t>
+  </si>
+  <si>
+    <t>The Little Explorer</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>The story reminded me to keep trying even when something is difficult.</t>
+  </si>
+  <si>
+    <t>Space for Kids</t>
+  </si>
+  <si>
+    <t>My favorite topic was planets.</t>
+  </si>
+  <si>
+    <t>book_002.jpg</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
     <t>Reading</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>Expression</t>
+  </si>
+  <si>
+    <t>SelfLearning</t>
+  </si>
+  <si>
+    <t>Creativity</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Started building regular reading habits.</t>
+  </si>
+  <si>
+    <t>More confident in sharing ideas and completing projects.</t>
+  </si>
+  <si>
+    <t>Shows stronger curiosity, expression, and independent learning.</t>
+  </si>
+  <si>
+    <t>MostImportantProgress</t>
+  </si>
+  <si>
+    <t>FavoriteProject</t>
+  </si>
+  <si>
+    <t>ImportantAwards</t>
+  </si>
+  <si>
+    <t>NextYearGoals</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>CoverImage</t>
+  </si>
+  <si>
+    <t>More confident speaking and presenting in front of others.</t>
+  </si>
+  <si>
+    <t>English Reading Contest - Second Place</t>
+  </si>
+  <si>
+    <t>Read more English books and complete two science projects.</t>
+  </si>
+  <si>
+    <t>A year of steady growth in reading, expression, and creativity.</t>
+  </si>
+  <si>
+    <t>review_2026.jpg</t>
+  </si>
+  <si>
+    <t>Built a stronger reading routine.</t>
+  </si>
+  <si>
+    <t>Animal Drawing Project</t>
+  </si>
+  <si>
+    <t>Creative Drawing Challenge - Excellent Work</t>
+  </si>
+  <si>
+    <t>Practice English speaking and keep a weekly reading log.</t>
+  </si>
+  <si>
+    <t>A year of building habits and discovering interests.</t>
+  </si>
+  <si>
+    <t>AllowedValues</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>Learning Category</t>
+  </si>
+  <si>
+    <t>Reading, School Activity, Science, English, Math, Art, Music, Sports, Coding, Life Skill, Other</t>
+  </si>
+  <si>
+    <t>Used in LearningTimeline.Category</t>
+  </si>
+  <si>
+    <t>Award Category</t>
+  </si>
+  <si>
+    <t>English, Math, Art, Science, Sports, Music, School, Community, Other</t>
+  </si>
+  <si>
+    <t>Used in Awards.Category</t>
+  </si>
+  <si>
+    <t>Project Category</t>
+  </si>
+  <si>
+    <t>Coding, Art, Science, Writing, Music, Video, Presentation, Other</t>
+  </si>
+  <si>
+    <t>Used in Projects.Category</t>
+  </si>
+  <si>
+    <t>Yes, No</t>
+  </si>
+  <si>
+    <t>Show item on the home page</t>
+  </si>
+  <si>
+    <t>Public-safe, Private</t>
+  </si>
+  <si>
+    <t>Use Public-safe for items that can be shared</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5</t>
+  </si>
+  <si>
+    <t>ReadingLog.Rating</t>
+  </si>
+  <si>
+    <t>Richard's Learning Journey - Data Dashboard</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Total Learning Records</t>
+  </si>
+  <si>
+    <t>Featured Learning Records</t>
+  </si>
+  <si>
+    <t>Total Awards</t>
+  </si>
+  <si>
+    <t>Total Projects</t>
+  </si>
+  <si>
+    <t>Total Books</t>
+  </si>
+  <si>
+    <t>Average Reading Rating</t>
+  </si>
+  <si>
+    <t>Finished an animal science book</t>
+  </si>
+  <si>
+    <t>Learned how insects adapt to different environments.</t>
+  </si>
+  <si>
+    <t>My favorite part was learning about beetles.</t>
+  </si>
+  <si>
+    <t>learning_001.jpg</t>
   </si>
   <si>
     <t>Public-safe</t>
   </si>
   <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>AwardName</t>
-  </si>
-  <si>
-    <t>AwardLevel</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>award_001.jpg</t>
+    <t>School Activity</t>
+  </si>
+  <si>
+    <t>Class presentation practice</t>
+  </si>
+  <si>
+    <t>Practiced speaking clearly and organizing ideas.</t>
+  </si>
+  <si>
+    <t>I felt more confident after practicing.</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Camp</t>
+  </si>
+  <si>
+    <t>Mario Detective &amp; Coin-Earning Little Boss Camp</t>
+  </si>
+  <si>
+    <t>Richard joined a playful camp that combined detective-style problem solving with money-themed activities. The experience helped him practice observation, logical thinking, decision-making, and basic financial awareness.</t>
+  </si>
+  <si>
+    <t>I practiced solving clues, making choices, and learning how to think like a little boss.</t>
+  </si>
+  <si>
+    <t>Musical Theatre Camp</t>
+  </si>
+  <si>
+    <t>Richard participated in a musical theatre camp and explored singing, movement, acting, and stage expression. The experience helped him build confidence, creativity, teamwork, and presentation skills.</t>
+  </si>
+  <si>
+    <t>I enjoyed expressing myself through music, movement, and performance.</t>
+  </si>
+  <si>
+    <t>Plant growth observation</t>
+  </si>
+  <si>
+    <t>Observed how light and water affect plant growth.</t>
+  </si>
+  <si>
+    <t>I learned to record small changes every day.</t>
+  </si>
+  <si>
+    <t>learning_002.jpg</t>
+  </si>
+  <si>
+    <t>SMC Regional Round</t>
+  </si>
+  <si>
+    <t>Marshall Cavendish Education (MCE)</t>
+  </si>
+  <si>
+    <t>Richard earned a Silver Award in the SMC Regional Round. The competition encouraged him to think carefully, stay focused, and challenge himself in mathematics.</t>
   </si>
   <si>
     <t>award_002.jpg</t>
   </si>
   <si>
-    <t>ProjectName</t>
-  </si>
-  <si>
-    <t>Tools</t>
-  </si>
-  <si>
-    <t>VideoLink</t>
-  </si>
-  <si>
-    <t>Scratch Fruit Catcher Game</t>
-  </si>
-  <si>
-    <t>project_001.jpg</t>
-  </si>
-  <si>
-    <t>BookTitle</t>
-  </si>
-  <si>
-    <t>Rating</t>
-  </si>
-  <si>
-    <t>book_002.jpg</t>
-  </si>
-  <si>
-    <t>Math</t>
-  </si>
-  <si>
-    <t>Expression</t>
-  </si>
-  <si>
-    <t>SelfLearning</t>
-  </si>
-  <si>
-    <t>Creativity</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Started building regular reading habits.</t>
-  </si>
-  <si>
-    <t>More confident in sharing ideas and completing projects.</t>
-  </si>
-  <si>
-    <t>Shows stronger curiosity, expression, and independent learning.</t>
-  </si>
-  <si>
-    <t>MostImportantProgress</t>
-  </si>
-  <si>
-    <t>FavoriteProject</t>
-  </si>
-  <si>
-    <t>ImportantAwards</t>
-  </si>
-  <si>
-    <t>NextYearGoals</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>CoverImage</t>
-  </si>
-  <si>
-    <t>More confident speaking and presenting in front of others.</t>
-  </si>
-  <si>
-    <t>English Reading Contest - Second Place</t>
-  </si>
-  <si>
-    <t>Read more English books and complete two science projects.</t>
-  </si>
-  <si>
-    <t>A year of steady growth in reading, expression, and creativity.</t>
-  </si>
-  <si>
-    <t>review_2026.jpg</t>
-  </si>
-  <si>
-    <t>Built a stronger reading routine.</t>
-  </si>
-  <si>
-    <t>Animal Drawing Project</t>
-  </si>
-  <si>
-    <t>Creative Drawing Challenge - Excellent Work</t>
-  </si>
-  <si>
-    <t>Practice English speaking and keep a weekly reading log.</t>
-  </si>
-  <si>
-    <t>A year of building habits and discovering interests.</t>
-  </si>
-  <si>
-    <t>AllowedValues</t>
-  </si>
-  <si>
-    <t>Usage</t>
-  </si>
-  <si>
-    <t>Learning Category</t>
-  </si>
-  <si>
-    <t>Reading, School Activity, Science, English, Math, Art, Music, Sports, Coding, Life Skill, Other</t>
-  </si>
-  <si>
-    <t>Used in LearningTimeline.Category</t>
-  </si>
-  <si>
-    <t>Award Category</t>
-  </si>
-  <si>
-    <t>English, Math, Art, Science, Sports, Music, School, Community, Other</t>
-  </si>
-  <si>
-    <t>Used in Awards.Category</t>
-  </si>
-  <si>
-    <t>Project Category</t>
-  </si>
-  <si>
-    <t>Coding, Art, Science, Writing, Music, Video, Presentation, Other</t>
-  </si>
-  <si>
-    <t>Used in Projects.Category</t>
-  </si>
-  <si>
-    <t>Yes, No</t>
-  </si>
-  <si>
-    <t>Show item on the home page</t>
-  </si>
-  <si>
-    <t>Public-safe, Private</t>
-  </si>
-  <si>
-    <t>Use Public-safe for items that can be shared</t>
-  </si>
-  <si>
-    <t>1, 2, 3, 4, 5</t>
-  </si>
-  <si>
-    <t>ReadingLog.Rating</t>
-  </si>
-  <si>
-    <t>Richard's Learning Journey - Data Dashboard</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>Total Learning Records</t>
-  </si>
-  <si>
-    <t>Featured Learning Records</t>
-  </si>
-  <si>
-    <t>Total Awards</t>
-  </si>
-  <si>
-    <t>Total Projects</t>
-  </si>
-  <si>
-    <t>Total Books</t>
-  </si>
-  <si>
-    <t>Average Reading Rating</t>
-  </si>
-  <si>
-    <t>MATH KANGAROO TAIWAN</t>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Athlete's Oath</t>
+  </si>
+  <si>
+    <t>Athlete's Oath Representative</t>
+  </si>
+  <si>
+    <t>Richard was selected to lead the athletes' oath at Horizon Field Day, representing fellow participants and highlighting sportsmanship and fair play.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Rope Skipping (G4 Boys)</t>
+  </si>
+  <si>
+    <t>1st Place</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' rope skipping event at Horizon Field Day, demonstrating coordination, speed, and focus.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Long Jump (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' long jump event at Horizon Field Day, showing determination and athletic ability.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Shuttle Run (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' shuttle run event at Horizon Field Day, demonstrating speed, agility, and focus.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Softball Throw (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' softball throw event at Horizon Field Day, demonstrating strength, technique, and concentration.</t>
+  </si>
+  <si>
+    <t>Boys' MVP</t>
+  </si>
+  <si>
+    <t>Richard was named Boys' MVP at Horizon Field Day in recognition of his outstanding overall performance across the sporting events.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Boys' MVP</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Association Kangourou sans Frontières</t>
+    <t>Horizon</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SMC Regional Round</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Silver</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Organizer</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Marshall Cavendish Education (MCE)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard participated in Math Kangaroo Taiwan and earned a Silver Award. This experience helped him build confidence in mathematical thinking and problem-solving.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard earned a Silver Award in the SMC Regional Round. The competition encouraged him to think carefully, stay focused, and challenge himself in mathematics.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>第63屆 奧林匹克數理競賽</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>金卓越銀獎</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>中華數學協會</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asian Gifted Education Association</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOP TALENT AWARD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>International Joint Schools Mathematics Competition (IJSMC)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard joined the International Joint Schools Mathematics Competition and received the Top Talent Award. This experience encouraged him to think deeply, solve problems with confidence, and enjoy mathematical challenges.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard participated in the 63rd Olympic Mathematics and Science Competition and received the Gold Excellence Silver Award. The experience helped him build focus, patience, and confidence in mathematical problem-solving.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Musical Theatre Camp</t>
-  </si>
-  <si>
-    <t>Camp</t>
-  </si>
-  <si>
-    <t>Richard participated in a musical theatre camp and explored singing, movement, acting, and stage expression. The experience helped him build confidence, creativity, teamwork, and presentation skills.</t>
-  </si>
-  <si>
-    <t>I enjoyed expressing myself through music, movement, and performance.</t>
-  </si>
-  <si>
-    <t>Mario Detective &amp; Coin-Earning Little Boss Camp</t>
-  </si>
-  <si>
-    <t>Richard joined a playful camp that combined detective-style problem solving with money-themed activities. The experience helped him practice observation, logical thinking, decision-making, and basic financial awareness.</t>
-  </si>
-  <si>
-    <t>I practiced solving clues, making choices, and learning how to think like a little boss.</t>
-  </si>
-  <si>
-    <t>Elementary School Student</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>This portfolio records Richard's learning journey, including his awards, camps, projects, reading, and yearly growth.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>This website uses a nickname only and avoids sharing personal information such as school name, class, address, or birthday.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Wild Robot Escapes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>book_003.jpg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Peter Brown</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Story</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wayside School</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Author</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Louis Sachar</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>book_001.jpg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Wild Robot</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Explorer</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>book_004.jpg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Katherine Rundell</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>A Star Multi Sport Camp</t>
-  </si>
-  <si>
-    <t>Richard participated in a multi-sport camp and experienced different physical activities through games, teamwork, and practice. The camp helped him develop coordination, confidence, sportsmanship, and perseverance.</t>
-  </si>
-  <si>
-    <t>I tried different sports, practiced with others, and learned to keep going even when the activities were challenging.</t>
-  </si>
-  <si>
-    <t>Film Camp</t>
-  </si>
-  <si>
-    <t>Richard joined a film camp and explored storytelling, acting, camera work, and creative expression. The experience helped him develop imagination, communication skills, teamwork, and confidence in presenting ideas.</t>
-  </si>
-  <si>
-    <t>I enjoyed creating stories, acting with others, and learning how ideas can become a film.</t>
-  </si>
-  <si>
-    <t>Flight Camp</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard participated in a flight camp that introduced the roles of pilots and cabin crew through hands-on training activities. The experience helped him understand aviation teamwork, safety, communication, and responsibility</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>I enjoyed learning about pilots and cabin crew, and I discovered how teamwork and responsibility are important in aviation.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> City Building, Energy, and Creativity</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard designed and built a creative city model with roads, railways, buildings, wind turbines, and solar panels. Through this project, he explored how a city works and learned about renewable energy, transportation, planning, and teamwork.</t>
   </si>
 </sst>
 </file>
@@ -540,7 +590,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,6 +607,11 @@
         <fgColor rgb="FFF2E8CF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B8F71"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -571,7 +626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -591,68 +646,35 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -676,25 +698,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LearningTimelineTable" displayName="LearningTimelineTable" ref="A1:J6" headerRowDxfId="6" dataDxfId="4" totalsRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LearningTimelineTable" displayName="LearningTimelineTable" ref="A1:J4">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Year" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Category" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Title" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Reflection" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Image" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Link" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Featured" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Privacy" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Year"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Category"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Title"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Description"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Reflection"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Image"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Link"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Featured"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Privacy"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AwardsTable" displayName="AwardsTable" ref="A1:J4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AwardsTable" displayName="AwardsTable" ref="A1:J11">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Year"/>
@@ -730,7 +752,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReadingLogTable" displayName="ReadingLogTable" ref="A1:I5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReadingLogTable" displayName="ReadingLogTable" ref="A1:I4">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Year"/>
@@ -831,9 +853,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -981,47 +1003,47 @@
         <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.5">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28.5">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5">
-        <v>46189</v>
+        <v>46187</v>
       </c>
     </row>
   </sheetData>
@@ -1035,187 +1057,2522 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="12" customWidth="1"/>
-    <col min="2" max="2" width="10" style="12" customWidth="1"/>
-    <col min="3" max="3" width="18" style="12" customWidth="1"/>
-    <col min="4" max="4" width="28" style="12" customWidth="1"/>
-    <col min="5" max="6" width="42" style="12" customWidth="1"/>
-    <col min="7" max="7" width="22" style="12" customWidth="1"/>
-    <col min="8" max="8" width="30" style="12" customWidth="1"/>
-    <col min="9" max="9" width="12" style="12" customWidth="1"/>
-    <col min="10" max="10" width="18" style="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
+    <col min="7" max="8" width="20" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15">
-      <c r="A1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="A1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="G1" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="71.25">
+      <c r="H1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B2" s="8">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57">
+      <c r="A4" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B4" s="8">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="42.75">
+      <c r="A5" s="6">
         <v>46125</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B5" s="8">
         <v>2026</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="71.25">
-      <c r="A3" s="6">
-        <v>46146</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="C5" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B6" s="8">
         <v>2026</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="85.5">
-      <c r="A4" s="5">
-        <v>46006</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2025</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="71.25">
-      <c r="A5" s="11">
-        <v>45999</v>
-      </c>
-      <c r="B5" s="12">
-        <v>2025</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="C6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="71.25">
-      <c r="A6" s="11">
-        <v>45887</v>
-      </c>
-      <c r="B6" s="12">
-        <v>2025</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>27</v>
-      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="11"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="11"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="11"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="11"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="11"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="11"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="11"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="11"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="11"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="11"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="11"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="11"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="11"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="11"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13"/>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="13"/>
+      <c r="J85" s="13"/>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="11"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="13"/>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="11"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13"/>
+      <c r="J94" s="13"/>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="13"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="13"/>
+      <c r="J95" s="13"/>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="13"/>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="11"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="13"/>
+      <c r="J97" s="13"/>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="11"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="13"/>
+      <c r="J98" s="13"/>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="11"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="13"/>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="11"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="11"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="13"/>
+      <c r="D102" s="13"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="11"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="13"/>
+      <c r="J103" s="13"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="13"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
+      <c r="I104" s="13"/>
+      <c r="J104" s="13"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="11"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="13"/>
+      <c r="J105" s="13"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
+      <c r="I106" s="13"/>
+      <c r="J106" s="13"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="11"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
+      <c r="I107" s="13"/>
+      <c r="J107" s="13"/>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="11"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="13"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="11"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
+      <c r="I109" s="13"/>
+      <c r="J109" s="13"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="11"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="13"/>
+      <c r="J110" s="13"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="11"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="13"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="13"/>
+      <c r="J111" s="13"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="11"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="13"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="11"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="13"/>
+      <c r="J113" s="13"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="11"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="13"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="13"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="11"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="13"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
+      <c r="I115" s="13"/>
+      <c r="J115" s="13"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="11"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="13"/>
+      <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
+      <c r="I116" s="13"/>
+      <c r="J116" s="13"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="11"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="13"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="13"/>
+      <c r="G117" s="13"/>
+      <c r="H117" s="13"/>
+      <c r="I117" s="13"/>
+      <c r="J117" s="13"/>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="11"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="13"/>
+      <c r="D118" s="13"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="13"/>
+      <c r="J118" s="13"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="11"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="13"/>
+      <c r="J119" s="13"/>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="11"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="13"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="13"/>
+      <c r="J120" s="13"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" s="11"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="13"/>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" s="11"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="13"/>
+      <c r="D122" s="13"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="11"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="13"/>
+      <c r="D123" s="13"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
+      <c r="I123" s="13"/>
+      <c r="J123" s="13"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="11"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="13"/>
+      <c r="D124" s="13"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="13"/>
+      <c r="J124" s="13"/>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="11"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="13"/>
+      <c r="D125" s="13"/>
+      <c r="E125" s="13"/>
+      <c r="F125" s="13"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
+      <c r="I125" s="13"/>
+      <c r="J125" s="13"/>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="11"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="13"/>
+      <c r="E126" s="13"/>
+      <c r="F126" s="13"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="13"/>
+      <c r="J126" s="13"/>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" s="11"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="13"/>
+      <c r="D127" s="13"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="13"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
+      <c r="I127" s="13"/>
+      <c r="J127" s="13"/>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" s="11"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="13"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="13"/>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
+      <c r="I128" s="13"/>
+      <c r="J128" s="13"/>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="11"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="13"/>
+      <c r="D129" s="13"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="13"/>
+      <c r="G129" s="13"/>
+      <c r="H129" s="13"/>
+      <c r="I129" s="13"/>
+      <c r="J129" s="13"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="11"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="13"/>
+      <c r="D130" s="13"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="13"/>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
+      <c r="I130" s="13"/>
+      <c r="J130" s="13"/>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="11"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="13"/>
+      <c r="D131" s="13"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="13"/>
+      <c r="G131" s="13"/>
+      <c r="H131" s="13"/>
+      <c r="I131" s="13"/>
+      <c r="J131" s="13"/>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="11"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="13"/>
+      <c r="D132" s="13"/>
+      <c r="E132" s="13"/>
+      <c r="F132" s="13"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
+      <c r="I132" s="13"/>
+      <c r="J132" s="13"/>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="11"/>
+      <c r="B133" s="12"/>
+      <c r="C133" s="13"/>
+      <c r="D133" s="13"/>
+      <c r="E133" s="13"/>
+      <c r="F133" s="13"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
+      <c r="I133" s="13"/>
+      <c r="J133" s="13"/>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="11"/>
+      <c r="B134" s="12"/>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="I134" s="13"/>
+      <c r="J134" s="13"/>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="11"/>
+      <c r="B135" s="12"/>
+      <c r="C135" s="13"/>
+      <c r="D135" s="13"/>
+      <c r="E135" s="13"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13"/>
+      <c r="I135" s="13"/>
+      <c r="J135" s="13"/>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" s="11"/>
+      <c r="B136" s="12"/>
+      <c r="C136" s="13"/>
+      <c r="D136" s="13"/>
+      <c r="E136" s="13"/>
+      <c r="F136" s="13"/>
+      <c r="G136" s="13"/>
+      <c r="H136" s="13"/>
+      <c r="I136" s="13"/>
+      <c r="J136" s="13"/>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" s="11"/>
+      <c r="B137" s="12"/>
+      <c r="C137" s="13"/>
+      <c r="D137" s="13"/>
+      <c r="E137" s="13"/>
+      <c r="F137" s="13"/>
+      <c r="G137" s="13"/>
+      <c r="H137" s="13"/>
+      <c r="I137" s="13"/>
+      <c r="J137" s="13"/>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" s="11"/>
+      <c r="B138" s="12"/>
+      <c r="C138" s="13"/>
+      <c r="D138" s="13"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="13"/>
+      <c r="G138" s="13"/>
+      <c r="H138" s="13"/>
+      <c r="I138" s="13"/>
+      <c r="J138" s="13"/>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" s="11"/>
+      <c r="B139" s="12"/>
+      <c r="C139" s="13"/>
+      <c r="D139" s="13"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="13"/>
+      <c r="G139" s="13"/>
+      <c r="H139" s="13"/>
+      <c r="I139" s="13"/>
+      <c r="J139" s="13"/>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" s="11"/>
+      <c r="B140" s="12"/>
+      <c r="C140" s="13"/>
+      <c r="D140" s="13"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="13"/>
+      <c r="G140" s="13"/>
+      <c r="H140" s="13"/>
+      <c r="I140" s="13"/>
+      <c r="J140" s="13"/>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" s="11"/>
+      <c r="B141" s="12"/>
+      <c r="C141" s="13"/>
+      <c r="D141" s="13"/>
+      <c r="E141" s="13"/>
+      <c r="F141" s="13"/>
+      <c r="G141" s="13"/>
+      <c r="H141" s="13"/>
+      <c r="I141" s="13"/>
+      <c r="J141" s="13"/>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" s="11"/>
+      <c r="B142" s="12"/>
+      <c r="C142" s="13"/>
+      <c r="D142" s="13"/>
+      <c r="E142" s="13"/>
+      <c r="F142" s="13"/>
+      <c r="G142" s="13"/>
+      <c r="H142" s="13"/>
+      <c r="I142" s="13"/>
+      <c r="J142" s="13"/>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" s="11"/>
+      <c r="B143" s="12"/>
+      <c r="C143" s="13"/>
+      <c r="D143" s="13"/>
+      <c r="E143" s="13"/>
+      <c r="F143" s="13"/>
+      <c r="G143" s="13"/>
+      <c r="H143" s="13"/>
+      <c r="I143" s="13"/>
+      <c r="J143" s="13"/>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" s="11"/>
+      <c r="B144" s="12"/>
+      <c r="C144" s="13"/>
+      <c r="D144" s="13"/>
+      <c r="E144" s="13"/>
+      <c r="F144" s="13"/>
+      <c r="G144" s="13"/>
+      <c r="H144" s="13"/>
+      <c r="I144" s="13"/>
+      <c r="J144" s="13"/>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" s="11"/>
+      <c r="B145" s="12"/>
+      <c r="C145" s="13"/>
+      <c r="D145" s="13"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="13"/>
+      <c r="G145" s="13"/>
+      <c r="H145" s="13"/>
+      <c r="I145" s="13"/>
+      <c r="J145" s="13"/>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" s="11"/>
+      <c r="B146" s="12"/>
+      <c r="C146" s="13"/>
+      <c r="D146" s="13"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="13"/>
+      <c r="G146" s="13"/>
+      <c r="H146" s="13"/>
+      <c r="I146" s="13"/>
+      <c r="J146" s="13"/>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" s="11"/>
+      <c r="B147" s="12"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
+      <c r="H147" s="13"/>
+      <c r="I147" s="13"/>
+      <c r="J147" s="13"/>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" s="11"/>
+      <c r="B148" s="12"/>
+      <c r="C148" s="13"/>
+      <c r="D148" s="13"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="13"/>
+      <c r="G148" s="13"/>
+      <c r="H148" s="13"/>
+      <c r="I148" s="13"/>
+      <c r="J148" s="13"/>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" s="11"/>
+      <c r="B149" s="12"/>
+      <c r="C149" s="13"/>
+      <c r="D149" s="13"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
+      <c r="H149" s="13"/>
+      <c r="I149" s="13"/>
+      <c r="J149" s="13"/>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" s="11"/>
+      <c r="B150" s="12"/>
+      <c r="C150" s="13"/>
+      <c r="D150" s="13"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
+      <c r="I150" s="13"/>
+      <c r="J150" s="13"/>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" s="11"/>
+      <c r="B151" s="12"/>
+      <c r="C151" s="13"/>
+      <c r="D151" s="13"/>
+      <c r="E151" s="13"/>
+      <c r="F151" s="13"/>
+      <c r="G151" s="13"/>
+      <c r="H151" s="13"/>
+      <c r="I151" s="13"/>
+      <c r="J151" s="13"/>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" s="11"/>
+      <c r="B152" s="12"/>
+      <c r="C152" s="13"/>
+      <c r="D152" s="13"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="13"/>
+      <c r="G152" s="13"/>
+      <c r="H152" s="13"/>
+      <c r="I152" s="13"/>
+      <c r="J152" s="13"/>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" s="11"/>
+      <c r="B153" s="12"/>
+      <c r="C153" s="13"/>
+      <c r="D153" s="13"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
+      <c r="I153" s="13"/>
+      <c r="J153" s="13"/>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" s="11"/>
+      <c r="B154" s="12"/>
+      <c r="C154" s="13"/>
+      <c r="D154" s="13"/>
+      <c r="E154" s="13"/>
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="13"/>
+      <c r="J154" s="13"/>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" s="11"/>
+      <c r="B155" s="12"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="I155" s="13"/>
+      <c r="J155" s="13"/>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" s="11"/>
+      <c r="B156" s="12"/>
+      <c r="C156" s="13"/>
+      <c r="D156" s="13"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="13"/>
+      <c r="G156" s="13"/>
+      <c r="H156" s="13"/>
+      <c r="I156" s="13"/>
+      <c r="J156" s="13"/>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" s="11"/>
+      <c r="B157" s="12"/>
+      <c r="C157" s="13"/>
+      <c r="D157" s="13"/>
+      <c r="E157" s="13"/>
+      <c r="F157" s="13"/>
+      <c r="G157" s="13"/>
+      <c r="H157" s="13"/>
+      <c r="I157" s="13"/>
+      <c r="J157" s="13"/>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" s="11"/>
+      <c r="B158" s="12"/>
+      <c r="C158" s="13"/>
+      <c r="D158" s="13"/>
+      <c r="E158" s="13"/>
+      <c r="F158" s="13"/>
+      <c r="G158" s="13"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="13"/>
+      <c r="J158" s="13"/>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" s="11"/>
+      <c r="B159" s="12"/>
+      <c r="C159" s="13"/>
+      <c r="D159" s="13"/>
+      <c r="E159" s="13"/>
+      <c r="F159" s="13"/>
+      <c r="G159" s="13"/>
+      <c r="H159" s="13"/>
+      <c r="I159" s="13"/>
+      <c r="J159" s="13"/>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" s="11"/>
+      <c r="B160" s="12"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="13"/>
+      <c r="J160" s="13"/>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" s="11"/>
+      <c r="B161" s="12"/>
+      <c r="C161" s="13"/>
+      <c r="D161" s="13"/>
+      <c r="E161" s="13"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="13"/>
+      <c r="H161" s="13"/>
+      <c r="I161" s="13"/>
+      <c r="J161" s="13"/>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" s="11"/>
+      <c r="B162" s="12"/>
+      <c r="C162" s="13"/>
+      <c r="D162" s="13"/>
+      <c r="E162" s="13"/>
+      <c r="F162" s="13"/>
+      <c r="G162" s="13"/>
+      <c r="H162" s="13"/>
+      <c r="I162" s="13"/>
+      <c r="J162" s="13"/>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" s="11"/>
+      <c r="B163" s="12"/>
+      <c r="C163" s="13"/>
+      <c r="D163" s="13"/>
+      <c r="E163" s="13"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="13"/>
+      <c r="H163" s="13"/>
+      <c r="I163" s="13"/>
+      <c r="J163" s="13"/>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" s="11"/>
+      <c r="B164" s="12"/>
+      <c r="C164" s="13"/>
+      <c r="D164" s="13"/>
+      <c r="E164" s="13"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="13"/>
+      <c r="H164" s="13"/>
+      <c r="I164" s="13"/>
+      <c r="J164" s="13"/>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" s="11"/>
+      <c r="B165" s="12"/>
+      <c r="C165" s="13"/>
+      <c r="D165" s="13"/>
+      <c r="E165" s="13"/>
+      <c r="F165" s="13"/>
+      <c r="G165" s="13"/>
+      <c r="H165" s="13"/>
+      <c r="I165" s="13"/>
+      <c r="J165" s="13"/>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" s="11"/>
+      <c r="B166" s="12"/>
+      <c r="C166" s="13"/>
+      <c r="D166" s="13"/>
+      <c r="E166" s="13"/>
+      <c r="F166" s="13"/>
+      <c r="G166" s="13"/>
+      <c r="H166" s="13"/>
+      <c r="I166" s="13"/>
+      <c r="J166" s="13"/>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" s="11"/>
+      <c r="B167" s="12"/>
+      <c r="C167" s="13"/>
+      <c r="D167" s="13"/>
+      <c r="E167" s="13"/>
+      <c r="F167" s="13"/>
+      <c r="G167" s="13"/>
+      <c r="H167" s="13"/>
+      <c r="I167" s="13"/>
+      <c r="J167" s="13"/>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" s="11"/>
+      <c r="B168" s="12"/>
+      <c r="C168" s="13"/>
+      <c r="D168" s="13"/>
+      <c r="E168" s="13"/>
+      <c r="F168" s="13"/>
+      <c r="G168" s="13"/>
+      <c r="H168" s="13"/>
+      <c r="I168" s="13"/>
+      <c r="J168" s="13"/>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" s="11"/>
+      <c r="B169" s="12"/>
+      <c r="C169" s="13"/>
+      <c r="D169" s="13"/>
+      <c r="E169" s="13"/>
+      <c r="F169" s="13"/>
+      <c r="G169" s="13"/>
+      <c r="H169" s="13"/>
+      <c r="I169" s="13"/>
+      <c r="J169" s="13"/>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" s="11"/>
+      <c r="B170" s="12"/>
+      <c r="C170" s="13"/>
+      <c r="D170" s="13"/>
+      <c r="E170" s="13"/>
+      <c r="F170" s="13"/>
+      <c r="G170" s="13"/>
+      <c r="H170" s="13"/>
+      <c r="I170" s="13"/>
+      <c r="J170" s="13"/>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" s="11"/>
+      <c r="B171" s="12"/>
+      <c r="C171" s="13"/>
+      <c r="D171" s="13"/>
+      <c r="E171" s="13"/>
+      <c r="F171" s="13"/>
+      <c r="G171" s="13"/>
+      <c r="H171" s="13"/>
+      <c r="I171" s="13"/>
+      <c r="J171" s="13"/>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" s="11"/>
+      <c r="B172" s="12"/>
+      <c r="C172" s="13"/>
+      <c r="D172" s="13"/>
+      <c r="E172" s="13"/>
+      <c r="F172" s="13"/>
+      <c r="G172" s="13"/>
+      <c r="H172" s="13"/>
+      <c r="I172" s="13"/>
+      <c r="J172" s="13"/>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" s="11"/>
+      <c r="B173" s="12"/>
+      <c r="C173" s="13"/>
+      <c r="D173" s="13"/>
+      <c r="E173" s="13"/>
+      <c r="F173" s="13"/>
+      <c r="G173" s="13"/>
+      <c r="H173" s="13"/>
+      <c r="I173" s="13"/>
+      <c r="J173" s="13"/>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" s="11"/>
+      <c r="B174" s="12"/>
+      <c r="C174" s="13"/>
+      <c r="D174" s="13"/>
+      <c r="E174" s="13"/>
+      <c r="F174" s="13"/>
+      <c r="G174" s="13"/>
+      <c r="H174" s="13"/>
+      <c r="I174" s="13"/>
+      <c r="J174" s="13"/>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" s="11"/>
+      <c r="B175" s="12"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="13"/>
+      <c r="E175" s="13"/>
+      <c r="F175" s="13"/>
+      <c r="G175" s="13"/>
+      <c r="H175" s="13"/>
+      <c r="I175" s="13"/>
+      <c r="J175" s="13"/>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" s="11"/>
+      <c r="B176" s="12"/>
+      <c r="C176" s="13"/>
+      <c r="D176" s="13"/>
+      <c r="E176" s="13"/>
+      <c r="F176" s="13"/>
+      <c r="G176" s="13"/>
+      <c r="H176" s="13"/>
+      <c r="I176" s="13"/>
+      <c r="J176" s="13"/>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" s="11"/>
+      <c r="B177" s="12"/>
+      <c r="C177" s="13"/>
+      <c r="D177" s="13"/>
+      <c r="E177" s="13"/>
+      <c r="F177" s="13"/>
+      <c r="G177" s="13"/>
+      <c r="H177" s="13"/>
+      <c r="I177" s="13"/>
+      <c r="J177" s="13"/>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" s="11"/>
+      <c r="B178" s="12"/>
+      <c r="C178" s="13"/>
+      <c r="D178" s="13"/>
+      <c r="E178" s="13"/>
+      <c r="F178" s="13"/>
+      <c r="G178" s="13"/>
+      <c r="H178" s="13"/>
+      <c r="I178" s="13"/>
+      <c r="J178" s="13"/>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" s="11"/>
+      <c r="B179" s="12"/>
+      <c r="C179" s="13"/>
+      <c r="D179" s="13"/>
+      <c r="E179" s="13"/>
+      <c r="F179" s="13"/>
+      <c r="G179" s="13"/>
+      <c r="H179" s="13"/>
+      <c r="I179" s="13"/>
+      <c r="J179" s="13"/>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" s="11"/>
+      <c r="B180" s="12"/>
+      <c r="C180" s="13"/>
+      <c r="D180" s="13"/>
+      <c r="E180" s="13"/>
+      <c r="F180" s="13"/>
+      <c r="G180" s="13"/>
+      <c r="H180" s="13"/>
+      <c r="I180" s="13"/>
+      <c r="J180" s="13"/>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" s="11"/>
+      <c r="B181" s="12"/>
+      <c r="C181" s="13"/>
+      <c r="D181" s="13"/>
+      <c r="E181" s="13"/>
+      <c r="F181" s="13"/>
+      <c r="G181" s="13"/>
+      <c r="H181" s="13"/>
+      <c r="I181" s="13"/>
+      <c r="J181" s="13"/>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" s="11"/>
+      <c r="B182" s="12"/>
+      <c r="C182" s="13"/>
+      <c r="D182" s="13"/>
+      <c r="E182" s="13"/>
+      <c r="F182" s="13"/>
+      <c r="G182" s="13"/>
+      <c r="H182" s="13"/>
+      <c r="I182" s="13"/>
+      <c r="J182" s="13"/>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" s="11"/>
+      <c r="B183" s="12"/>
+      <c r="C183" s="13"/>
+      <c r="D183" s="13"/>
+      <c r="E183" s="13"/>
+      <c r="F183" s="13"/>
+      <c r="G183" s="13"/>
+      <c r="H183" s="13"/>
+      <c r="I183" s="13"/>
+      <c r="J183" s="13"/>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" s="11"/>
+      <c r="B184" s="12"/>
+      <c r="C184" s="13"/>
+      <c r="D184" s="13"/>
+      <c r="E184" s="13"/>
+      <c r="F184" s="13"/>
+      <c r="G184" s="13"/>
+      <c r="H184" s="13"/>
+      <c r="I184" s="13"/>
+      <c r="J184" s="13"/>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" s="11"/>
+      <c r="B185" s="12"/>
+      <c r="C185" s="13"/>
+      <c r="D185" s="13"/>
+      <c r="E185" s="13"/>
+      <c r="F185" s="13"/>
+      <c r="G185" s="13"/>
+      <c r="H185" s="13"/>
+      <c r="I185" s="13"/>
+      <c r="J185" s="13"/>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" s="11"/>
+      <c r="B186" s="12"/>
+      <c r="C186" s="13"/>
+      <c r="D186" s="13"/>
+      <c r="E186" s="13"/>
+      <c r="F186" s="13"/>
+      <c r="G186" s="13"/>
+      <c r="H186" s="13"/>
+      <c r="I186" s="13"/>
+      <c r="J186" s="13"/>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187" s="11"/>
+      <c r="B187" s="12"/>
+      <c r="C187" s="13"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="13"/>
+      <c r="F187" s="13"/>
+      <c r="G187" s="13"/>
+      <c r="H187" s="13"/>
+      <c r="I187" s="13"/>
+      <c r="J187" s="13"/>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188" s="11"/>
+      <c r="B188" s="12"/>
+      <c r="C188" s="13"/>
+      <c r="D188" s="13"/>
+      <c r="E188" s="13"/>
+      <c r="F188" s="13"/>
+      <c r="G188" s="13"/>
+      <c r="H188" s="13"/>
+      <c r="I188" s="13"/>
+      <c r="J188" s="13"/>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" s="11"/>
+      <c r="B189" s="12"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="13"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
+      <c r="H189" s="13"/>
+      <c r="I189" s="13"/>
+      <c r="J189" s="13"/>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" s="11"/>
+      <c r="B190" s="12"/>
+      <c r="C190" s="13"/>
+      <c r="D190" s="13"/>
+      <c r="E190" s="13"/>
+      <c r="F190" s="13"/>
+      <c r="G190" s="13"/>
+      <c r="H190" s="13"/>
+      <c r="I190" s="13"/>
+      <c r="J190" s="13"/>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" s="11"/>
+      <c r="B191" s="12"/>
+      <c r="C191" s="13"/>
+      <c r="D191" s="13"/>
+      <c r="E191" s="13"/>
+      <c r="F191" s="13"/>
+      <c r="G191" s="13"/>
+      <c r="H191" s="13"/>
+      <c r="I191" s="13"/>
+      <c r="J191" s="13"/>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" s="11"/>
+      <c r="B192" s="12"/>
+      <c r="C192" s="13"/>
+      <c r="D192" s="13"/>
+      <c r="E192" s="13"/>
+      <c r="F192" s="13"/>
+      <c r="G192" s="13"/>
+      <c r="H192" s="13"/>
+      <c r="I192" s="13"/>
+      <c r="J192" s="13"/>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" s="11"/>
+      <c r="B193" s="12"/>
+      <c r="C193" s="13"/>
+      <c r="D193" s="13"/>
+      <c r="E193" s="13"/>
+      <c r="F193" s="13"/>
+      <c r="G193" s="13"/>
+      <c r="H193" s="13"/>
+      <c r="I193" s="13"/>
+      <c r="J193" s="13"/>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" s="11"/>
+      <c r="B194" s="12"/>
+      <c r="C194" s="13"/>
+      <c r="D194" s="13"/>
+      <c r="E194" s="13"/>
+      <c r="F194" s="13"/>
+      <c r="G194" s="13"/>
+      <c r="H194" s="13"/>
+      <c r="I194" s="13"/>
+      <c r="J194" s="13"/>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" s="11"/>
+      <c r="B195" s="12"/>
+      <c r="C195" s="13"/>
+      <c r="D195" s="13"/>
+      <c r="E195" s="13"/>
+      <c r="F195" s="13"/>
+      <c r="G195" s="13"/>
+      <c r="H195" s="13"/>
+      <c r="I195" s="13"/>
+      <c r="J195" s="13"/>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" s="11"/>
+      <c r="B196" s="12"/>
+      <c r="C196" s="13"/>
+      <c r="D196" s="13"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="13"/>
+      <c r="G196" s="13"/>
+      <c r="H196" s="13"/>
+      <c r="I196" s="13"/>
+      <c r="J196" s="13"/>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" s="11"/>
+      <c r="B197" s="12"/>
+      <c r="C197" s="13"/>
+      <c r="D197" s="13"/>
+      <c r="E197" s="13"/>
+      <c r="F197" s="13"/>
+      <c r="G197" s="13"/>
+      <c r="H197" s="13"/>
+      <c r="I197" s="13"/>
+      <c r="J197" s="13"/>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" s="11"/>
+      <c r="B198" s="12"/>
+      <c r="C198" s="13"/>
+      <c r="D198" s="13"/>
+      <c r="E198" s="13"/>
+      <c r="F198" s="13"/>
+      <c r="G198" s="13"/>
+      <c r="H198" s="13"/>
+      <c r="I198" s="13"/>
+      <c r="J198" s="13"/>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" s="11"/>
+      <c r="B199" s="12"/>
+      <c r="C199" s="13"/>
+      <c r="D199" s="13"/>
+      <c r="E199" s="13"/>
+      <c r="F199" s="13"/>
+      <c r="G199" s="13"/>
+      <c r="H199" s="13"/>
+      <c r="I199" s="13"/>
+      <c r="J199" s="13"/>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200" s="11"/>
+      <c r="B200" s="12"/>
+      <c r="C200" s="13"/>
+      <c r="D200" s="13"/>
+      <c r="E200" s="13"/>
+      <c r="F200" s="13"/>
+      <c r="G200" s="13"/>
+      <c r="H200" s="13"/>
+      <c r="I200" s="13"/>
+      <c r="J200" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1239,7 +3596,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1256,34 +3613,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="71.25">
@@ -1294,24 +3651,24 @@
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42.75">
@@ -1322,26 +3679,26 @@
         <v>2026</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="71.25">
@@ -1352,54 +3709,207 @@
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="42.75">
-      <c r="A5" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="54" customHeight="1">
+      <c r="A5" s="6">
         <v>46145</v>
       </c>
       <c r="B5" s="4">
         <v>2026</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>94</v>
+        <v>31</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>149</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>100</v>
+        <v>150</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="54" customHeight="1">
+      <c r="A6" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B6">
+        <v>2026</v>
+      </c>
+      <c r="C6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="54" customHeight="1">
+      <c r="A7" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B7">
+        <v>2026</v>
+      </c>
+      <c r="C7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="54" customHeight="1">
+      <c r="A8" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B8">
+        <v>2026</v>
+      </c>
+      <c r="C8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="54" customHeight="1">
+      <c r="A9" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B9">
+        <v>2026</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="54" customHeight="1">
+      <c r="A10" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B10">
+        <v>2026</v>
+      </c>
+      <c r="C10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="54" customHeight="1">
+      <c r="A11" s="7">
+        <v>46312</v>
+      </c>
+      <c r="B11">
+        <v>2026</v>
+      </c>
+      <c r="C11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="J11" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1436,85 +3946,117 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="28.5">
       <c r="A2" s="5">
-        <v>46121</v>
+        <v>46181</v>
       </c>
       <c r="B2" s="4">
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="G2" s="4" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="A3" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28.5">
+      <c r="A4" s="5">
+        <v>46086</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1535,7 +4077,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1551,137 +4093,116 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5">
-        <v>45908</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="G2" s="4">
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="28.5">
       <c r="A3" s="5">
-        <v>45658</v>
+        <v>46156</v>
       </c>
       <c r="B3" s="4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F3" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="G3" s="4">
-        <v>5</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>126</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="5">
-        <v>46027</v>
+        <v>46115</v>
       </c>
       <c r="B4" s="4">
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="G4" s="4">
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="5">
-        <v>46153</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2026</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
-        <v>5</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G5 G6:G200" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="G2:G200" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1707,28 +4228,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D1" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1754,7 +4275,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1780,7 +4301,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1806,7 +4327,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1834,25 +4355,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5">
@@ -1860,22 +4381,22 @@
         <v>2026</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1883,19 +4404,19 @@
         <v>2025</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -1920,79 +4441,79 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.5">
       <c r="A2" s="4" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2014,26 +4535,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="A1" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3">
         <f>COUNTA(LearningTimeline!D2:D200)</f>
@@ -2042,47 +4563,47 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
         <f>COUNTIF(LearningTimeline!I2:I200,"Yes")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3">
-        <f>COUNTA(Awards!D3:D200)</f>
-        <v>3</v>
+        <f>COUNTA(Awards!D2:D200)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTA(Projects!D2:D200)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="B8" s="3">
-        <f>COUNTA(ReadingLog!C5:C200)</f>
-        <v>1</v>
+        <f>COUNTA(ReadingLog!C2:C200)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="B9" s="3">
-        <f>IFERROR(AVERAGE(ReadingLog!G5:G200),0)</f>
-        <v>5</v>
+        <f>IFERROR(AVERAGE(ReadingLog!G2:G200),0)</f>
+        <v>4.666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2091,6 +4612,5 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711151BE-6D95-4C00-A498-6F73CADD12BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69C2246-5C86-4B2B-AEBB-8481441B6AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3793,16 +3793,16 @@
         <v>153</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F7" t="s">
         <v>169</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -3897,16 +3897,16 @@
         <v>153</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F11" t="s">
         <v>169</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="J11" t="s">
         <v>36</v>
@@ -3915,10 +3915,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C2 C3:C200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="C2:C7 C8:C200" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"English,Math,Art,Science,Sports,Music,School,Community,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2 J3:J200" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="J2:J7 J8:J200" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YuHui\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69C2246-5C86-4B2B-AEBB-8481441B6AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3B25C0-289E-4F73-BF2B-C4AF62593B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="169">
   <si>
     <t>Field</t>
   </si>
@@ -514,19 +514,19 @@
     <t>Richard was selected to lead the athletes' oath at Horizon Field Day, representing fellow participants and highlighting sportsmanship and fair play.</t>
   </si>
   <si>
-    <t>Horizon Field Day – Rope Skipping (G4 Boys)</t>
+    <t>Horizon Field Day – Jump Rope (G4 Boys)</t>
   </si>
   <si>
     <t>1st Place</t>
   </si>
   <si>
-    <t>Richard won first place in the Grade 4 boys' rope skipping event at Horizon Field Day, demonstrating coordination, speed, and focus.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Long Jump (G4 Boys)</t>
-  </si>
-  <si>
-    <t>Richard won first place in the Grade 4 boys' long jump event at Horizon Field Day, showing determination and athletic ability.</t>
+    <t>Richard won first place in the Grade 4 boys' jump rope event at Horizon Field Day, demonstrating coordination, speed, and focus.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Standing Long Jump (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' standing long jump event at Horizon Field Day, showing determination and athletic ability.</t>
   </si>
   <si>
     <t>Horizon Field Day – Shuttle Run (G4 Boys)</t>
@@ -535,24 +535,19 @@
     <t>Richard won first place in the Grade 4 boys' shuttle run event at Horizon Field Day, demonstrating speed, agility, and focus.</t>
   </si>
   <si>
-    <t>Horizon Field Day – Softball Throw (G4 Boys)</t>
-  </si>
-  <si>
-    <t>Richard won first place in the Grade 4 boys' softball throw event at Horizon Field Day, demonstrating strength, technique, and concentration.</t>
+    <t>Horizon Field Day – Ball Throw (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' ball throw event at Horizon Field Day, demonstrating strength, technique, and concentration.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Boys' MVP</t>
   </si>
   <si>
     <t>Boys' MVP</t>
   </si>
   <si>
     <t>Richard was named Boys' MVP at Horizon Field Day in recognition of his outstanding overall performance across the sporting events.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Boys' MVP</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Horizon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3793,16 +3788,13 @@
         <v>153</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>168</v>
-      </c>
-      <c r="E7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>167</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -3824,9 +3816,6 @@
       <c r="E8" t="s">
         <v>158</v>
       </c>
-      <c r="F8" t="s">
-        <v>169</v>
-      </c>
       <c r="G8" s="13" t="s">
         <v>161</v>
       </c>
@@ -3845,16 +3834,13 @@
         <v>153</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
         <v>158</v>
       </c>
-      <c r="F9" t="s">
-        <v>169</v>
-      </c>
       <c r="G9" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J9" t="s">
         <v>36</v>
@@ -3871,16 +3857,13 @@
         <v>153</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
         <v>158</v>
       </c>
-      <c r="F10" t="s">
-        <v>169</v>
-      </c>
       <c r="G10" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J10" t="s">
         <v>36</v>
@@ -3902,9 +3885,6 @@
       <c r="E11" t="s">
         <v>158</v>
       </c>
-      <c r="F11" t="s">
-        <v>169</v>
-      </c>
       <c r="G11" s="13" t="s">
         <v>159</v>
       </c>
@@ -3915,10 +3895,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C2:C7 C8:C200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="C11:C200 C2:C10" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"English,Math,Art,Science,Sports,Music,School,Community,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J7 J8:J200" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="J11:J200 J2:J10" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YuHui\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3B25C0-289E-4F73-BF2B-C4AF62593B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACAB9BC-5029-4498-9743-4DE8663377BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="175">
   <si>
     <t>Field</t>
   </si>
@@ -205,36 +205,9 @@
     <t>project_001.jpg</t>
   </si>
   <si>
-    <t>Art</t>
-  </si>
-  <si>
-    <t>My Favorite Animal Drawing</t>
-  </si>
-  <si>
-    <t>An illustrated animal drawing with a short description.</t>
-  </si>
-  <si>
-    <t>Color pencils</t>
-  </si>
-  <si>
-    <t>project_002.jpg</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Science</t>
   </si>
   <si>
-    <t>Mini Weather Chart</t>
-  </si>
-  <si>
-    <t>Recorded weather changes and summarized temperature patterns.</t>
-  </si>
-  <si>
-    <t>Notebook, chart</t>
-  </si>
-  <si>
     <t>BookTitle</t>
   </si>
   <si>
@@ -244,310 +217,371 @@
     <t>Rating</t>
   </si>
   <si>
-    <t>Amazing Insects</t>
-  </si>
-  <si>
-    <t>Sample Author</t>
-  </si>
-  <si>
-    <t>I learned that insects use many ways to protect themselves.</t>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>book_002.jpg</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>Expression</t>
+  </si>
+  <si>
+    <t>SelfLearning</t>
+  </si>
+  <si>
+    <t>Creativity</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Started building regular reading habits.</t>
+  </si>
+  <si>
+    <t>More confident in sharing ideas and completing projects.</t>
+  </si>
+  <si>
+    <t>Shows stronger curiosity, expression, and independent learning.</t>
+  </si>
+  <si>
+    <t>MostImportantProgress</t>
+  </si>
+  <si>
+    <t>FavoriteProject</t>
+  </si>
+  <si>
+    <t>ImportantAwards</t>
+  </si>
+  <si>
+    <t>NextYearGoals</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>CoverImage</t>
+  </si>
+  <si>
+    <t>More confident speaking and presenting in front of others.</t>
+  </si>
+  <si>
+    <t>English Reading Contest - Second Place</t>
+  </si>
+  <si>
+    <t>Read more English books and complete two science projects.</t>
+  </si>
+  <si>
+    <t>A year of steady growth in reading, expression, and creativity.</t>
+  </si>
+  <si>
+    <t>review_2026.jpg</t>
+  </si>
+  <si>
+    <t>Built a stronger reading routine.</t>
+  </si>
+  <si>
+    <t>Animal Drawing Project</t>
+  </si>
+  <si>
+    <t>Creative Drawing Challenge - Excellent Work</t>
+  </si>
+  <si>
+    <t>Practice English speaking and keep a weekly reading log.</t>
+  </si>
+  <si>
+    <t>A year of building habits and discovering interests.</t>
+  </si>
+  <si>
+    <t>AllowedValues</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>Learning Category</t>
+  </si>
+  <si>
+    <t>Used in LearningTimeline.Category</t>
+  </si>
+  <si>
+    <t>Award Category</t>
+  </si>
+  <si>
+    <t>Used in Awards.Category</t>
+  </si>
+  <si>
+    <t>Project Category</t>
+  </si>
+  <si>
+    <t>Coding, Art, Science, Writing, Music, Video, Presentation, Other</t>
+  </si>
+  <si>
+    <t>Used in Projects.Category</t>
+  </si>
+  <si>
+    <t>Yes, No</t>
+  </si>
+  <si>
+    <t>Show item on the home page</t>
+  </si>
+  <si>
+    <t>Public-safe, Private</t>
+  </si>
+  <si>
+    <t>Use Public-safe for items that can be shared</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5</t>
+  </si>
+  <si>
+    <t>ReadingLog.Rating</t>
+  </si>
+  <si>
+    <t>Richard's Learning Journey - Data Dashboard</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Total Learning Records</t>
+  </si>
+  <si>
+    <t>Featured Learning Records</t>
+  </si>
+  <si>
+    <t>Total Awards</t>
+  </si>
+  <si>
+    <t>Total Projects</t>
+  </si>
+  <si>
+    <t>Total Books</t>
+  </si>
+  <si>
+    <t>Average Reading Rating</t>
+  </si>
+  <si>
+    <t>Public-safe</t>
+  </si>
+  <si>
+    <t>Camp</t>
+  </si>
+  <si>
+    <t>Mario Detective &amp; Coin-Earning Little Boss Camp</t>
+  </si>
+  <si>
+    <t>Richard joined a playful camp that combined detective-style problem solving with money-themed activities. The experience helped him practice observation, logical thinking, decision-making, and basic financial awareness.</t>
+  </si>
+  <si>
+    <t>I practiced solving clues, making choices, and learning how to think like a little boss.</t>
+  </si>
+  <si>
+    <t>Musical Theatre Camp</t>
+  </si>
+  <si>
+    <t>Richard participated in a musical theatre camp and explored singing, movement, acting, and stage expression. The experience helped him build confidence, creativity, teamwork, and presentation skills.</t>
+  </si>
+  <si>
+    <t>I enjoyed expressing myself through music, movement, and performance.</t>
+  </si>
+  <si>
+    <t>Plant growth observation</t>
+  </si>
+  <si>
+    <t>Observed how light and water affect plant growth.</t>
+  </si>
+  <si>
+    <t>I learned to record small changes every day.</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>DELF Prim A1.1 Certificate Presentation</t>
+  </si>
+  <si>
+    <t>After passing the DELF Prim A1.1 French language examination in April 2026, Richard received his certificate from the president of Alliance Française de Taiwan on September 17, 2026.</t>
+  </si>
+  <si>
+    <t>SMC Regional Round</t>
+  </si>
+  <si>
+    <t>Marshall Cavendish Education (MCE)</t>
+  </si>
+  <si>
+    <t>Richard earned a Silver Award in the SMC Regional Round. The competition encouraged him to think carefully, stay focused, and challenge himself in mathematics.</t>
+  </si>
+  <si>
+    <t>award_002.jpg</t>
+  </si>
+  <si>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Boys' MVP</t>
+  </si>
+  <si>
+    <t>Boys' MVP</t>
+  </si>
+  <si>
+    <t>Richard was named Boys' MVP at Horizon Field Day in recognition of his outstanding overall performance across the sporting events.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Athlete's Oath</t>
+  </si>
+  <si>
+    <t>Athlete's Oath Representative</t>
+  </si>
+  <si>
+    <t>Richard was selected to lead the athletes' oath at Horizon Field Day, representing fellow participants and highlighting sportsmanship and fair play.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Standing Long Jump (G4 Boys)</t>
+  </si>
+  <si>
+    <t>1st Place</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' standing long jump event at Horizon Field Day, showing determination and athletic ability.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Shuttle Run (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' shuttle run event at Horizon Field Day, demonstrating speed, agility, and focus.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Ball Throw (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' ball throw event at Horizon Field Day, demonstrating strength, technique, and concentration.</t>
+  </si>
+  <si>
+    <t>Horizon Field Day – Jump Rope (G4 Boys)</t>
+  </si>
+  <si>
+    <t>Richard won first place in the Grade 4 boys' jump rope event at Horizon Field Day, demonstrating coordination, speed, and focus.</t>
+  </si>
+  <si>
+    <t>DELF Prim A1.1 French Language Examination</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Alliance Française de Taiwan</t>
+  </si>
+  <si>
+    <t>Richard passed the DELF Prim A1.1 French language examination in April 2026. On September 17, 2026, he received his certificate from the president of Alliance Française de Taiwan.</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>The Last Bear</t>
+  </si>
+  <si>
+    <t>Hannah Gold</t>
+  </si>
+  <si>
+    <t>Reading, School Activity, Science, English, French, Math, Art, Music, Sports, Coding, Life Skill, Other</t>
+  </si>
+  <si>
+    <t>English, French, Math, Art, Science, Sports, Music, School, Community, Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> City Building, Energy, and Creativity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Richard designed and built a creative city model with roads, railways, buildings, wind turbines, and solar panels. Through this project, he explored how a city works and learned about renewable energy, transportation, planning, and teamwork.</t>
+  </si>
+  <si>
+    <t>The Explorer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Katherine Rundell</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Story</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>book_004.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wayside School</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Louis Sachar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>book_001.jpg</t>
-  </si>
-  <si>
-    <t>The Little Explorer</t>
-  </si>
-  <si>
-    <t>Story</t>
-  </si>
-  <si>
-    <t>The story reminded me to keep trying even when something is difficult.</t>
-  </si>
-  <si>
-    <t>Space for Kids</t>
-  </si>
-  <si>
-    <t>My favorite topic was planets.</t>
-  </si>
-  <si>
-    <t>book_002.jpg</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Expression</t>
-  </si>
-  <si>
-    <t>SelfLearning</t>
-  </si>
-  <si>
-    <t>Creativity</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Started building regular reading habits.</t>
-  </si>
-  <si>
-    <t>More confident in sharing ideas and completing projects.</t>
-  </si>
-  <si>
-    <t>Shows stronger curiosity, expression, and independent learning.</t>
-  </si>
-  <si>
-    <t>MostImportantProgress</t>
-  </si>
-  <si>
-    <t>FavoriteProject</t>
-  </si>
-  <si>
-    <t>ImportantAwards</t>
-  </si>
-  <si>
-    <t>NextYearGoals</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>CoverImage</t>
-  </si>
-  <si>
-    <t>More confident speaking and presenting in front of others.</t>
-  </si>
-  <si>
-    <t>English Reading Contest - Second Place</t>
-  </si>
-  <si>
-    <t>Read more English books and complete two science projects.</t>
-  </si>
-  <si>
-    <t>A year of steady growth in reading, expression, and creativity.</t>
-  </si>
-  <si>
-    <t>review_2026.jpg</t>
-  </si>
-  <si>
-    <t>Built a stronger reading routine.</t>
-  </si>
-  <si>
-    <t>Animal Drawing Project</t>
-  </si>
-  <si>
-    <t>Creative Drawing Challenge - Excellent Work</t>
-  </si>
-  <si>
-    <t>Practice English speaking and keep a weekly reading log.</t>
-  </si>
-  <si>
-    <t>A year of building habits and discovering interests.</t>
-  </si>
-  <si>
-    <t>AllowedValues</t>
-  </si>
-  <si>
-    <t>Usage</t>
-  </si>
-  <si>
-    <t>Learning Category</t>
-  </si>
-  <si>
-    <t>Reading, School Activity, Science, English, Math, Art, Music, Sports, Coding, Life Skill, Other</t>
-  </si>
-  <si>
-    <t>Used in LearningTimeline.Category</t>
-  </si>
-  <si>
-    <t>Award Category</t>
-  </si>
-  <si>
-    <t>English, Math, Art, Science, Sports, Music, School, Community, Other</t>
-  </si>
-  <si>
-    <t>Used in Awards.Category</t>
-  </si>
-  <si>
-    <t>Project Category</t>
-  </si>
-  <si>
-    <t>Coding, Art, Science, Writing, Music, Video, Presentation, Other</t>
-  </si>
-  <si>
-    <t>Used in Projects.Category</t>
-  </si>
-  <si>
-    <t>Yes, No</t>
-  </si>
-  <si>
-    <t>Show item on the home page</t>
-  </si>
-  <si>
-    <t>Public-safe, Private</t>
-  </si>
-  <si>
-    <t>Use Public-safe for items that can be shared</t>
-  </si>
-  <si>
-    <t>1, 2, 3, 4, 5</t>
-  </si>
-  <si>
-    <t>ReadingLog.Rating</t>
-  </si>
-  <si>
-    <t>Richard's Learning Journey - Data Dashboard</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>Total Learning Records</t>
-  </si>
-  <si>
-    <t>Featured Learning Records</t>
-  </si>
-  <si>
-    <t>Total Awards</t>
-  </si>
-  <si>
-    <t>Total Projects</t>
-  </si>
-  <si>
-    <t>Total Books</t>
-  </si>
-  <si>
-    <t>Average Reading Rating</t>
-  </si>
-  <si>
-    <t>Finished an animal science book</t>
-  </si>
-  <si>
-    <t>Learned how insects adapt to different environments.</t>
-  </si>
-  <si>
-    <t>My favorite part was learning about beetles.</t>
-  </si>
-  <si>
-    <t>learning_001.jpg</t>
-  </si>
-  <si>
-    <t>Public-safe</t>
-  </si>
-  <si>
-    <t>School Activity</t>
-  </si>
-  <si>
-    <t>Class presentation practice</t>
-  </si>
-  <si>
-    <t>Practiced speaking clearly and organizing ideas.</t>
-  </si>
-  <si>
-    <t>I felt more confident after practicing.</t>
-  </si>
-  <si>
-    <t>Private</t>
-  </si>
-  <si>
-    <t>Camp</t>
-  </si>
-  <si>
-    <t>Mario Detective &amp; Coin-Earning Little Boss Camp</t>
-  </si>
-  <si>
-    <t>Richard joined a playful camp that combined detective-style problem solving with money-themed activities. The experience helped him practice observation, logical thinking, decision-making, and basic financial awareness.</t>
-  </si>
-  <si>
-    <t>I practiced solving clues, making choices, and learning how to think like a little boss.</t>
-  </si>
-  <si>
-    <t>Musical Theatre Camp</t>
-  </si>
-  <si>
-    <t>Richard participated in a musical theatre camp and explored singing, movement, acting, and stage expression. The experience helped him build confidence, creativity, teamwork, and presentation skills.</t>
-  </si>
-  <si>
-    <t>I enjoyed expressing myself through music, movement, and performance.</t>
-  </si>
-  <si>
-    <t>Plant growth observation</t>
-  </si>
-  <si>
-    <t>Observed how light and water affect plant growth.</t>
-  </si>
-  <si>
-    <t>I learned to record small changes every day.</t>
-  </si>
-  <si>
-    <t>learning_002.jpg</t>
-  </si>
-  <si>
-    <t>SMC Regional Round</t>
-  </si>
-  <si>
-    <t>Marshall Cavendish Education (MCE)</t>
-  </si>
-  <si>
-    <t>Richard earned a Silver Award in the SMC Regional Round. The competition encouraged him to think carefully, stay focused, and challenge himself in mathematics.</t>
-  </si>
-  <si>
-    <t>award_002.jpg</t>
-  </si>
-  <si>
-    <t>Sports</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Athlete's Oath</t>
-  </si>
-  <si>
-    <t>Athlete's Oath Representative</t>
-  </si>
-  <si>
-    <t>Richard was selected to lead the athletes' oath at Horizon Field Day, representing fellow participants and highlighting sportsmanship and fair play.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Jump Rope (G4 Boys)</t>
-  </si>
-  <si>
-    <t>1st Place</t>
-  </si>
-  <si>
-    <t>Richard won first place in the Grade 4 boys' jump rope event at Horizon Field Day, demonstrating coordination, speed, and focus.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Standing Long Jump (G4 Boys)</t>
-  </si>
-  <si>
-    <t>Richard won first place in the Grade 4 boys' standing long jump event at Horizon Field Day, showing determination and athletic ability.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Shuttle Run (G4 Boys)</t>
-  </si>
-  <si>
-    <t>Richard won first place in the Grade 4 boys' shuttle run event at Horizon Field Day, demonstrating speed, agility, and focus.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Ball Throw (G4 Boys)</t>
-  </si>
-  <si>
-    <t>Richard won first place in the Grade 4 boys' ball throw event at Horizon Field Day, demonstrating strength, technique, and concentration.</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Boys' MVP</t>
-  </si>
-  <si>
-    <t>Boys' MVP</t>
-  </si>
-  <si>
-    <t>Richard was named Boys' MVP at Horizon Field Day in recognition of his outstanding overall performance across the sporting events.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Wild Robot</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peter Brown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Wild Robot Escapes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>book_003.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Last Bear.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Film Camp</t>
+  </si>
+  <si>
+    <t>Richard joined a film camp and explored storytelling, acting, camera work, and creative expression. The experience helped him develop imagination, communication skills, teamwork, and confidence in presenting ideas.</t>
+  </si>
+  <si>
+    <t>I enjoyed creating stories, acting with others, and learning how ideas can become a film.</t>
+  </si>
+  <si>
+    <t>A Star Multi Sport Camp</t>
+  </si>
+  <si>
+    <t>Richard participated in a multi-sport camp and experienced different physical activities through games, teamwork, and practice. The camp helped him develop coordination, confidence, sportsmanship, and perseverance.</t>
+  </si>
+  <si>
+    <t>I tried different sports, practiced with others, and learned to keep going even when the activities were challenging.</t>
+  </si>
+  <si>
+    <t>Flight Camp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Richard participated in a flight camp that introduced the roles of pilots and cabin crew through hands-on training activities. The experience helped him understand aviation teamwork, safety, communication, and responsibility</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>I enjoyed learning about pilots and cabin crew, and I discovered how teamwork and responsibility are important in aviation.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -557,7 +591,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -584,6 +618,11 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -608,7 +647,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -616,12 +655,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -660,10 +710,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -693,7 +750,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LearningTimelineTable" displayName="LearningTimelineTable" ref="A1:J4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="LearningTimelineTable" displayName="LearningTimelineTable" ref="A1:J5">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Year"/>
@@ -747,7 +804,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReadingLogTable" displayName="ReadingLogTable" ref="A1:I4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReadingLogTable" displayName="ReadingLogTable" ref="A1:I6">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Year"/>
@@ -1052,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J201"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1097,110 +1154,108 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B2" s="8">
-        <v>2026</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>128</v>
+    <row r="2" spans="1:10" ht="57">
+      <c r="A2" s="18">
+        <v>45887</v>
+      </c>
+      <c r="B2" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="6">
-        <v>46162</v>
-      </c>
-      <c r="B3" s="8">
-        <v>2026</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>134</v>
+      <c r="J2" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57">
+      <c r="A3" s="18">
+        <v>45999</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>137</v>
+        <v>171</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
+        <v>46006</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="57">
+      <c r="A5" s="6">
         <v>46146</v>
-      </c>
-      <c r="B4" s="8">
-        <v>2026</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="42.75">
-      <c r="A5" s="6">
-        <v>46125</v>
       </c>
       <c r="B5" s="8">
         <v>2026</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1208,62 +1263,90 @@
         <v>36</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="42.75">
       <c r="A6" s="6">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B6" s="8">
         <v>2026</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>148</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="A7" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B7" s="8">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="42.75">
+      <c r="A8" s="11">
+        <v>46282</v>
+      </c>
+      <c r="B8" s="12">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+      <c r="I8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11"/>
@@ -3569,16 +3652,28 @@
       <c r="I200" s="13"/>
       <c r="J200" s="13"/>
     </row>
+    <row r="201" spans="1:10">
+      <c r="A201" s="11"/>
+      <c r="B201" s="12"/>
+      <c r="C201" s="13"/>
+      <c r="D201" s="13"/>
+      <c r="E201" s="13"/>
+      <c r="F201" s="13"/>
+      <c r="G201" s="13"/>
+      <c r="H201" s="13"/>
+      <c r="I201" s="13"/>
+      <c r="J201" s="13"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="C2:C200" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="list" sqref="C2:C201" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Reading,School Activity,Science,English,Math,Art,Music,Sports,Coding,Life Skill,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I200" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="I2:I201" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J200" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="J2:J201" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Public-safe,Private"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3591,7 +3686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3735,19 +3830,19 @@
         <v>31</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
@@ -3762,16 +3857,16 @@
         <v>2026</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="J6" t="s">
         <v>36</v>
@@ -3785,16 +3880,16 @@
         <v>2026</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -3808,16 +3903,16 @@
         <v>2026</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="J8" t="s">
         <v>36</v>
@@ -3831,16 +3926,16 @@
         <v>2026</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="J9" t="s">
         <v>36</v>
@@ -3854,16 +3949,16 @@
         <v>2026</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="J10" t="s">
         <v>36</v>
@@ -3877,28 +3972,54 @@
         <v>2026</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="7">
+        <v>46282</v>
+      </c>
+      <c r="B12">
+        <v>2026</v>
+      </c>
+      <c r="C12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+      <c r="J12" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C11:C200 C2:C10" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="C2 C3:C200" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"English,Math,Art,Science,Sports,Music,School,Community,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J11:J200 J2:J10" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="J2 J3:J200" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3956,25 +4077,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="28.5">
+    <row r="2" spans="1:10" ht="71.25">
       <c r="A2" s="5">
-        <v>46181</v>
+        <v>46121</v>
       </c>
       <c r="B2" s="4">
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
         <v>53</v>
       </c>
@@ -3984,59 +4103,43 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="28.5">
       <c r="A3" s="5">
-        <v>46137</v>
+        <v>46181</v>
       </c>
       <c r="B3" s="4">
         <v>2026</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>58</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="28.5">
-      <c r="A4" s="5">
-        <v>46086</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2026</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="J4" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -4057,7 +4160,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4079,10 +4182,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>21</v>
@@ -4091,7 +4194,7 @@
         <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>24</v>
@@ -4102,87 +4205,137 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5">
-        <v>46174</v>
+        <v>45908</v>
       </c>
       <c r="B2" s="4">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4">
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="28.5">
+    <row r="3" spans="1:9">
       <c r="A3" s="5">
-        <v>46156</v>
+        <v>45658</v>
       </c>
       <c r="B3" s="4">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4">
-        <v>4</v>
-      </c>
-      <c r="H3" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="5">
-        <v>46115</v>
+        <v>46027</v>
       </c>
       <c r="B4" s="4">
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>161</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4">
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5">
+        <v>46153</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2:G200" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="G2:G202" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4211,25 +4364,25 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4255,7 +4408,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4281,7 +4434,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4307,7 +4460,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4338,22 +4491,22 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5">
@@ -4361,22 +4514,22 @@
         <v>2026</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4384,19 +4537,19 @@
         <v>2025</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4424,43 +4577,43 @@
         <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.5">
       <c r="A2" s="4" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.5">
       <c r="A3" s="4" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4468,10 +4621,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4479,21 +4632,21 @@
         <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -4515,75 +4668,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B4" s="3">
-        <f>COUNTA(LearningTimeline!D2:D200)</f>
-        <v>5</v>
+        <f>COUNTA(LearningTimeline!D2:D201)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(LearningTimeline!I2:I200,"Yes")</f>
-        <v>4</v>
+        <f>COUNTIF(LearningTimeline!I2:I201,"Yes")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTA(Awards!D2:D200)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTA(Projects!D2:D200)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B8" s="3">
-        <f>COUNTA(ReadingLog!C2:C200)</f>
-        <v>3</v>
+        <f>COUNTA(ReadingLog!C7:C202)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B9" s="3">
-        <f>IFERROR(AVERAGE(ReadingLog!G2:G200),0)</f>
-        <v>4.666666666666667</v>
+        <f>IFERROR(AVERAGE(ReadingLog!G7:G202),0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACAB9BC-5029-4498-9743-4DE8663377BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800E0365-15B6-45F7-AC74-A30D4329A28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -550,10 +550,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>The Last Bear.jpg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Film Camp</t>
   </si>
   <si>
@@ -581,6 +577,10 @@
   </si>
   <si>
     <t>I enjoyed learning about pilots and cabin crew, and I discovered how teamwork and responsibility are important in aviation.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The_Last_Bear.jpg</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -711,16 +711,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1155,7 +1155,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>45887</v>
       </c>
       <c r="B2" s="13">
@@ -1165,13 +1165,13 @@
         <v>110</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
@@ -1183,7 +1183,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="57">
-      <c r="A3" s="18">
+      <c r="A3" s="16">
         <v>45999</v>
       </c>
       <c r="B3" s="13">
@@ -1193,13 +1193,13 @@
         <v>110</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -1221,13 +1221,13 @@
         <v>110</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -3860,13 +3860,13 @@
         <v>127</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J6" t="s">
         <v>36</v>
@@ -3883,13 +3883,13 @@
         <v>127</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -4016,10 +4016,10 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="C2 C3:C200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="C8:C200 C2:C7" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"English,Math,Art,Science,Sports,Music,School,Community,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2 J3:J200" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="J8:J200 J2:J7" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4324,13 +4324,13 @@
         <v>5</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="14"/>
-      <c r="E7" s="17"/>
+      <c r="E7" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -4668,14 +4668,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">

--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C02BA2-DFE4-4D77-994F-D29002145A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0E498C-0C77-4E05-91EB-A1A5A8539F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="180">
   <si>
     <t>Field</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>MATH KANGAROO TAIWAN</t>
-  </si>
-  <si>
     <t>Silver</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t>Richard participated in Math Kangaroo Taiwan and earned a Silver Award. This experience helped him build confidence in mathematical thinking and problem-solving.</t>
   </si>
   <si>
-    <t>award_001.jpg</t>
-  </si>
-  <si>
     <t>第63屆 奧林匹克數理競賽</t>
   </si>
   <si>
@@ -421,22 +415,13 @@
     <t>https://heyzine.com/flip-book/9991bced10.html</t>
   </si>
   <si>
-    <t>SMC Regional Round</t>
-  </si>
-  <si>
     <t>Marshall Cavendish Education (MCE)</t>
   </si>
   <si>
     <t>Richard earned a Silver Award in the SMC Regional Round. The competition encouraged him to think carefully, stay focused, and challenge himself in mathematics.</t>
   </si>
   <si>
-    <t>award_002.jpg</t>
-  </si>
-  <si>
     <t>Sports</t>
-  </si>
-  <si>
-    <t>Horizon Field Day – Boys' MVP</t>
   </si>
   <si>
     <t>Boys' MVP</t>
@@ -596,6 +581,26 @@
   </si>
   <si>
     <t>20261025_Performance.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATH KANGAROO TAIWAN</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMC Regional Round</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026_SMC_Regional_Round.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Horizon Field Day – Boys' MVP</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026_Horizon_Field_Day.jpg</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -879,6 +884,7 @@
         <name val="Carlito"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -897,7 +903,6 @@
         <name val="Carlito"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -978,17 +983,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReadingLogTable" displayName="ReadingLogTable" ref="A1:I6" dataDxfId="0" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ReadingLogTable" displayName="ReadingLogTable" ref="A1:I6" dataDxfId="9" dataCellStyle="Normal">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Date" dataDxfId="9" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Year" dataDxfId="8" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="BookTitle" dataDxfId="7" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Author" dataDxfId="6" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Category" dataDxfId="5" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Reflection" dataDxfId="4" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Rating" dataDxfId="3" dataCellStyle="Normal"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Image" dataDxfId="2" dataCellStyle="Normal"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Link" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Date" dataDxfId="8" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Year" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="BookTitle" dataDxfId="6" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Author" dataDxfId="5" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Category" dataDxfId="4" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Reflection" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Rating" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Image" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Link" dataDxfId="0" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1316,7 +1321,7 @@
         <v>23</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>25</v>
@@ -1336,16 +1341,16 @@
         <v>2025</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
@@ -1353,7 +1358,7 @@
         <v>36</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57">
@@ -1364,16 +1369,16 @@
         <v>2025</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -1381,7 +1386,7 @@
         <v>36</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57">
@@ -1392,16 +1397,16 @@
         <v>2025</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -1409,7 +1414,7 @@
         <v>36</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="57">
@@ -1420,16 +1425,16 @@
         <v>2026</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1437,7 +1442,7 @@
         <v>36</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="42.75">
@@ -1448,16 +1453,16 @@
         <v>2026</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -1465,7 +1470,7 @@
         <v>36</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1476,16 +1481,16 @@
         <v>2026</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -1493,7 +1498,7 @@
         <v>36</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="42.75">
@@ -1504,13 +1509,13 @@
         <v>2026</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -1519,7 +1524,7 @@
         <v>36</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="57">
@@ -1530,26 +1535,26 @@
         <v>2026</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>122</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>124</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>36</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3952,20 +3957,18 @@
         <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
         <v>36</v>
@@ -3982,16 +3985,16 @@
         <v>31</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -4010,19 +4013,19 @@
         <v>31</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
@@ -4037,16 +4040,19 @@
         <v>2026</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>133</v>
+        <v>128</v>
+      </c>
+      <c r="H6" t="s">
+        <v>179</v>
       </c>
       <c r="J6" t="s">
         <v>36</v>
@@ -4060,16 +4066,19 @@
         <v>2026</v>
       </c>
       <c r="C7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" t="s">
         <v>130</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" t="s">
-        <v>135</v>
-      </c>
       <c r="G7" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
+      </c>
+      <c r="H7" t="s">
+        <v>179</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -4083,16 +4092,19 @@
         <v>2026</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
+      </c>
+      <c r="H8" t="s">
+        <v>179</v>
       </c>
       <c r="J8" t="s">
         <v>36</v>
@@ -4106,16 +4118,19 @@
         <v>2026</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>141</v>
+        <v>136</v>
+      </c>
+      <c r="H9" t="s">
+        <v>179</v>
       </c>
       <c r="J9" t="s">
         <v>36</v>
@@ -4129,16 +4144,19 @@
         <v>2026</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>143</v>
+      <c r="H10" t="s">
+        <v>179</v>
       </c>
       <c r="J10" t="s">
         <v>36</v>
@@ -4152,16 +4170,19 @@
         <v>2026</v>
       </c>
       <c r="C11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
+      </c>
+      <c r="H11" t="s">
+        <v>179</v>
       </c>
       <c r="J11" t="s">
         <v>36</v>
@@ -4175,19 +4196,19 @@
         <v>2026</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J12" t="s">
         <v>36</v>
@@ -4236,19 +4257,19 @@
         <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>25</v>
@@ -4265,17 +4286,17 @@
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -4291,16 +4312,16 @@
         <v>2026</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -4350,10 +4371,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>21</v>
@@ -4362,7 +4383,7 @@
         <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>24</v>
@@ -4379,20 +4400,20 @@
         <v>2025</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -4404,20 +4425,20 @@
         <v>2025</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
         <v>5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -4429,20 +4450,20 @@
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -4454,20 +4475,20 @@
         <v>2026</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <v>5</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -4479,20 +4500,20 @@
         <v>2026</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
         <v>5</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -4528,25 +4549,25 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4572,7 +4593,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4598,7 +4619,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4624,7 +4645,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4655,22 +4676,22 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5">
@@ -4678,22 +4699,22 @@
         <v>2026</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4701,19 +4722,19 @@
         <v>2025</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4741,43 +4762,43 @@
         <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.5">
       <c r="A2" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.5">
       <c r="A3" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4785,10 +4806,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4796,21 +4817,21 @@
         <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -4833,7 +4854,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
       <c r="A1" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4843,15 +4864,15 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" s="3">
         <f>COUNTA(LearningTimeline!D2:D200)</f>
@@ -4860,7 +4881,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3">
         <f>COUNTIF(LearningTimeline!I2:I200,"Yes")</f>
@@ -4869,7 +4890,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTA(Awards!D2:D200)</f>
@@ -4878,7 +4899,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTA(Projects!D2:D199)</f>
@@ -4887,7 +4908,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTA(ReadingLog!C2:C201)</f>
@@ -4896,7 +4917,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B9" s="3">
         <f>IFERROR(AVERAGE(ReadingLog!G2:G201),0)</f>

--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0E498C-0C77-4E05-91EB-A1A5A8539F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61F16F-AA45-41EC-8A7A-A6E074E7A628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="183">
   <si>
     <t>Field</t>
   </si>
@@ -139,9 +139,6 @@
     <t>Math</t>
   </si>
   <si>
-    <t>International Joint Schools Mathematics Competition (IJSMC)</t>
-  </si>
-  <si>
     <t>TOP TALENT AWARD</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>Richard participated in Math Kangaroo Taiwan and earned a Silver Award. This experience helped him build confidence in mathematical thinking and problem-solving.</t>
   </si>
   <si>
-    <t>第63屆 奧林匹克數理競賽</t>
-  </si>
-  <si>
     <t>金卓越銀獎</t>
   </si>
   <si>
@@ -464,9 +458,6 @@
   </si>
   <si>
     <t>Richard won first place in the Grade 4 boys' jump rope event at Horizon Field Day, demonstrating coordination, speed, and focus.</t>
-  </si>
-  <si>
-    <t>DELF Prim A1.1 French Language Examination</t>
   </si>
   <si>
     <t>Passed</t>
@@ -601,6 +592,72 @@
   </si>
   <si>
     <t>2026_Horizon_Field_Day.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026_Math_Kangaroo.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELF Prim A1.1 French Language Examination</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026_FEI_DELF_Prim_CMJN.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>63</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>屆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>奧林匹克數理競賽</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026_WOLPC.jpg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>International Joint Schools Mathematics Competition (IJSMC)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -611,7 +668,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -636,6 +693,23 @@
       <sz val="9"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -675,7 +749,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -718,6 +792,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1321,7 +1398,7 @@
         <v>23</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>25</v>
@@ -1341,24 +1418,24 @@
         <v>2025</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57">
@@ -1369,24 +1446,24 @@
         <v>2025</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57">
@@ -1397,24 +1474,24 @@
         <v>2025</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="57">
@@ -1425,24 +1502,24 @@
         <v>2026</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="42.75">
@@ -1453,24 +1530,24 @@
         <v>2026</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D6" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1481,24 +1558,24 @@
         <v>2026</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="42.75">
@@ -1509,22 +1586,22 @@
         <v>2026</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="57">
@@ -1535,26 +1612,26 @@
         <v>2026</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>122</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3929,21 +4006,21 @@
         <v>31</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="42.75">
@@ -3957,21 +4034,23 @@
         <v>31</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="71.25">
@@ -3984,22 +4063,24 @@
       <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="54" customHeight="1">
@@ -4013,23 +4094,23 @@
         <v>31</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="54" customHeight="1">
@@ -4040,22 +4121,22 @@
         <v>2026</v>
       </c>
       <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="H6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1">
@@ -4066,22 +4147,22 @@
         <v>2026</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D7" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="H7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="54" customHeight="1">
@@ -4092,22 +4173,22 @@
         <v>2026</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D8" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>134</v>
-      </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="54" customHeight="1">
@@ -4118,22 +4199,22 @@
         <v>2026</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="54" customHeight="1">
@@ -4144,22 +4225,22 @@
         <v>2026</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="54" customHeight="1">
@@ -4170,22 +4251,22 @@
         <v>2026</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="57">
@@ -4196,22 +4277,25 @@
         <v>2026</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="E12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>144</v>
+      <c r="H12" t="s">
+        <v>179</v>
       </c>
       <c r="J12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -4257,19 +4341,19 @@
         <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>25</v>
@@ -4286,22 +4370,22 @@
         <v>2026</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="28.5">
@@ -4312,22 +4396,22 @@
         <v>2026</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -4371,10 +4455,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>21</v>
@@ -4383,7 +4467,7 @@
         <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>24</v>
@@ -4400,20 +4484,20 @@
         <v>2025</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4">
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I2" s="4"/>
     </row>
@@ -4425,20 +4509,20 @@
         <v>2025</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4">
         <v>5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -4450,20 +4534,20 @@
         <v>2026</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -4475,20 +4559,20 @@
         <v>2026</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <v>5</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -4500,20 +4584,20 @@
         <v>2026</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4">
         <v>5</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -4549,25 +4633,25 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4593,7 +4677,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4619,7 +4703,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4645,7 +4729,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4676,22 +4760,22 @@
         <v>20</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.5">
@@ -4699,22 +4783,22 @@
         <v>2026</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4722,19 +4806,19 @@
         <v>2025</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4762,43 +4846,43 @@
         <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.5">
       <c r="A2" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.5">
       <c r="A3" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4806,10 +4890,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4817,21 +4901,21 @@
         <v>27</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4854,7 +4938,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
       <c r="A1" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4864,15 +4948,15 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" s="3">
         <f>COUNTA(LearningTimeline!D2:D200)</f>
@@ -4881,7 +4965,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <f>COUNTIF(LearningTimeline!I2:I200,"Yes")</f>
@@ -4890,7 +4974,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3">
         <f>COUNTA(Awards!D2:D200)</f>
@@ -4899,7 +4983,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTA(Projects!D2:D199)</f>
@@ -4908,7 +4992,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTA(ReadingLog!C2:C201)</f>
@@ -4917,7 +5001,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B9" s="3">
         <f>IFERROR(AVERAGE(ReadingLog!G2:G201),0)</f>

--- a/data/learning_portfolio.xlsx
+++ b/data/learning_portfolio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\88_YuHui\Streamlit\Richard_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61F16F-AA45-41EC-8A7A-A6E074E7A628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC540F5A-D281-4C0A-B27F-428B0AEBDE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="183">
   <si>
     <t>Field</t>
   </si>
@@ -788,13 +788,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1595,7 +1595,9 @@
         <v>117</v>
       </c>
       <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>179</v>
+      </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="s">
         <v>35</v>
@@ -4063,7 +4065,7 @@
       <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>180</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -4937,14 +4939,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="1" t="s">
